--- a/feedback_surveys/047_personal_organizer_feedback_form--feedback_surveys.xlsx
+++ b/feedback_surveys/047_personal_organizer_feedback_form--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat positive'}</t>
+          <t>Somewhat positive</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_negative'}</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat negative'}</t>
+          <t>Somewhat negative</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very negative'}</t>
+          <t>Very negative</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely satisfied'}</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_dissatisfied'}</t>
+          <t>extremely_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely dissatisfied'}</t>
+          <t>Extremely dissatisfied</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_useful'}</t>
+          <t>very_useful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very useful'}</t>
+          <t>Very useful</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_useful'}</t>
+          <t>somewhat_useful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat useful'}</t>
+          <t>Somewhat useful</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_useless'}</t>
+          <t>somewhat_useless</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat useless'}</t>
+          <t>Somewhat useless</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_useless'}</t>
+          <t>very_useless</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very useless'}</t>
+          <t>Very useless</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
